--- a/output/2026-08-24/enriched_analysis.xlsx
+++ b/output/2026-08-24/enriched_analysis.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gandhar Oil Refinery (India) Limited</t>
+          <t>GANDHAR OIL REFINERY (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1290,27 +1290,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PNGSREVA</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PNGS Reva Diamond Jewellery Limited</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Buy on Breakout</t>
+          <t>Strong Buy Setup</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G9" t="n">
         <v>20</v>
@@ -1319,82 +1319,84 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>547.45</v>
+        <v>67.88</v>
       </c>
       <c r="J9" t="n">
-        <v>390.61</v>
+        <v>70.27</v>
       </c>
       <c r="K9" t="n">
-        <v>40.2</v>
+        <v>-3.4</v>
       </c>
       <c r="L9" t="n">
-        <v>63.09</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>8.02</v>
+        <v>0.7</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.467</v>
+        <v>0.347</v>
       </c>
       <c r="Q9" t="n">
-        <v>1716</v>
+        <v>202</v>
       </c>
       <c r="R9" t="n">
-        <v>20.3</v>
+        <v>8.58</v>
       </c>
       <c r="S9" t="n">
-        <v>581</v>
+        <v>17</v>
       </c>
       <c r="T9" t="n">
-        <v>34</v>
+        <v>27.97</v>
       </c>
       <c r="U9" t="n">
-        <v>881</v>
+        <v>17</v>
       </c>
       <c r="V9" t="n">
-        <v>8.58</v>
+        <v>2.73</v>
       </c>
       <c r="W9" t="n">
-        <v>22</v>
+        <v>13.7</v>
       </c>
       <c r="X9" t="n">
-        <v>0.33</v>
+        <v>1.86</v>
       </c>
       <c r="Y9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>29</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AA9" t="n">
-        <v>450.64</v>
-      </c>
-      <c r="AB9" t="inlineStr"/>
+        <v>53.82</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>51.03</v>
+      </c>
       <c r="AC9" t="n">
-        <v>31.4</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>PNGSREVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>PNGS Reva Diamond Jewellery Limited</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1405,7 +1407,7 @@
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G10" t="n">
         <v>20</v>
@@ -1414,69 +1416,67 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>67.88</v>
+        <v>547.45</v>
       </c>
       <c r="J10" t="n">
-        <v>68.84999999999999</v>
+        <v>390.61</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4</v>
+        <v>40.2</v>
       </c>
       <c r="L10" t="n">
-        <v>72.56999999999999</v>
+        <v>63.09</v>
       </c>
       <c r="M10" t="n">
-        <v>0.46</v>
+        <v>8.02</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.228</v>
+        <v>0.467</v>
       </c>
       <c r="Q10" t="n">
-        <v>202</v>
+        <v>1716</v>
       </c>
       <c r="R10" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>581</v>
+      </c>
+      <c r="T10" t="n">
+        <v>34</v>
+      </c>
+      <c r="U10" t="n">
+        <v>881</v>
+      </c>
+      <c r="V10" t="n">
         <v>8.58</v>
       </c>
-      <c r="S10" t="n">
-        <v>17</v>
-      </c>
-      <c r="T10" t="n">
-        <v>27.97</v>
-      </c>
-      <c r="U10" t="n">
-        <v>17</v>
-      </c>
-      <c r="V10" t="n">
-        <v>2.73</v>
-      </c>
       <c r="W10" t="n">
-        <v>13.7</v>
+        <v>22</v>
       </c>
       <c r="X10" t="n">
-        <v>1.86</v>
+        <v>0.33</v>
       </c>
       <c r="Y10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.140000000000001</v>
+        <v>29</v>
       </c>
       <c r="AA10" t="n">
-        <v>53.82</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>51.03</v>
-      </c>
+        <v>450.64</v>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>41.3</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="11">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INE577L01016</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ganesh Consumer Products Limited</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OBCL LIMITED</t>
+          <t>OBCL LIMITED (FORMERLY KNOWN AS ORISSA BENGAL CARRIER LIMITED)</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gandhar Oil Refinery (India) Limited</t>
+          <t>GANDHAR OIL REFINERY (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5257,70 +5257,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PNGSREVA</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PNGS Reva Diamond Jewellery Limited</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>547.45</v>
+        <v>67.88</v>
       </c>
       <c r="D9" t="n">
-        <v>390.61</v>
+        <v>70.27</v>
       </c>
       <c r="E9" t="n">
-        <v>40.2</v>
+        <v>-3.4</v>
       </c>
       <c r="F9" t="n">
-        <v>63.09</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>8.02</v>
+        <v>0.7</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>PNGSREVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>PNGS Reva Diamond Jewellery Limited</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>67.88</v>
+        <v>547.45</v>
       </c>
       <c r="D10" t="n">
-        <v>68.84999999999999</v>
+        <v>390.61</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4</v>
+        <v>40.2</v>
       </c>
       <c r="F10" t="n">
-        <v>72.56999999999999</v>
+        <v>63.09</v>
       </c>
       <c r="G10" t="n">
-        <v>0.46</v>
+        <v>8.02</v>
       </c>
       <c r="H10" t="n">
         <v>3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INE577L01016</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ganesh Consumer Products Limited</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OBCL LIMITED</t>
+          <t>OBCL LIMITED (FORMERLY KNOWN AS ORISSA BENGAL CARRIER LIMITED)</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">

--- a/output/2026-08-24/enriched_analysis.xlsx
+++ b/output/2026-08-24/enriched_analysis.xlsx
@@ -640,13 +640,13 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>256</v>
+        <v>256.62</v>
       </c>
       <c r="J2" t="n">
         <v>158.6</v>
       </c>
       <c r="K2" t="n">
-        <v>61.4</v>
+        <v>61.8</v>
       </c>
       <c r="L2" t="n">
         <v>64.63</v>
@@ -737,13 +737,13 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>88</v>
+        <v>89.12</v>
       </c>
       <c r="J3" t="n">
         <v>55.67</v>
       </c>
       <c r="K3" t="n">
-        <v>58.1</v>
+        <v>60.1</v>
       </c>
       <c r="L3" t="n">
         <v>67.45999999999999</v>
@@ -834,13 +834,13 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>5484</v>
+        <v>5493.5</v>
       </c>
       <c r="J4" t="n">
         <v>5085.36</v>
       </c>
       <c r="K4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
         <v>67.16</v>
@@ -931,13 +931,13 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1960</v>
+        <v>1963.4</v>
       </c>
       <c r="J5" t="n">
         <v>920.51</v>
       </c>
       <c r="K5" t="n">
-        <v>112.9</v>
+        <v>113.3</v>
       </c>
       <c r="L5" t="n">
         <v>73.16</v>
@@ -1028,13 +1028,13 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>822.3</v>
+        <v>816.9</v>
       </c>
       <c r="J6" t="n">
         <v>753.55</v>
       </c>
       <c r="K6" t="n">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="L6" t="n">
         <v>69.61</v>
@@ -1222,13 +1222,13 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>368.5</v>
+        <v>371.75</v>
       </c>
       <c r="J8" t="n">
         <v>335.41</v>
       </c>
       <c r="K8" t="n">
-        <v>9.9</v>
+        <v>10.8</v>
       </c>
       <c r="L8" t="n">
         <v>68.48</v>
@@ -1319,13 +1319,13 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>67.88</v>
+        <v>68.55</v>
       </c>
       <c r="J9" t="n">
         <v>70.27</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.4</v>
+        <v>-2.4</v>
       </c>
       <c r="L9" t="n">
         <v>72.56999999999999</v>
@@ -1416,13 +1416,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>547.45</v>
+        <v>541.05</v>
       </c>
       <c r="J10" t="n">
         <v>390.61</v>
       </c>
       <c r="K10" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="L10" t="n">
         <v>63.09</v>
@@ -1511,13 +1511,13 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>190</v>
+        <v>193.72</v>
       </c>
       <c r="J11" t="n">
         <v>164.1</v>
       </c>
       <c r="K11" t="n">
-        <v>15.8</v>
+        <v>18</v>
       </c>
       <c r="L11" t="n">
         <v>60.6</v>
@@ -1606,13 +1606,13 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>372.1</v>
+        <v>376.15</v>
       </c>
       <c r="J12" t="n">
         <v>338.1</v>
       </c>
       <c r="K12" t="n">
-        <v>10.1</v>
+        <v>11.3</v>
       </c>
       <c r="L12" t="n">
         <v>66.73</v>
@@ -1703,13 +1703,13 @@
         <v>-2</v>
       </c>
       <c r="I13" t="n">
-        <v>625</v>
+        <v>617.6</v>
       </c>
       <c r="J13" t="n">
         <v>558.6799999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>11.9</v>
+        <v>10.5</v>
       </c>
       <c r="L13" t="n">
         <v>64.68000000000001</v>
@@ -1897,13 +1897,13 @@
         <v>-3</v>
       </c>
       <c r="I15" t="n">
-        <v>271</v>
+        <v>273.91</v>
       </c>
       <c r="J15" t="n">
         <v>230</v>
       </c>
       <c r="K15" t="n">
-        <v>17.8</v>
+        <v>19.1</v>
       </c>
       <c r="L15" t="n">
         <v>67.65000000000001</v>
@@ -1994,13 +1994,13 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>20.4</v>
+        <v>20.09</v>
       </c>
       <c r="J16" t="n">
         <v>21.01</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.9</v>
+        <v>-4.4</v>
       </c>
       <c r="L16" t="n">
         <v>70.87</v>
@@ -2087,13 +2087,13 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>131.15</v>
+        <v>132.32</v>
       </c>
       <c r="J17" t="n">
         <v>100.9</v>
       </c>
       <c r="K17" t="n">
-        <v>30</v>
+        <v>31.1</v>
       </c>
       <c r="L17" t="n">
         <v>69.56</v>
@@ -2184,13 +2184,13 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>774.5</v>
+        <v>770.35</v>
       </c>
       <c r="J18" t="n">
         <v>716.01</v>
       </c>
       <c r="K18" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="L18" t="n">
         <v>61.71</v>
@@ -2279,13 +2279,13 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>112.5</v>
+        <v>113.43</v>
       </c>
       <c r="J19" t="n">
         <v>109.31</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="L19" t="n">
         <v>72.34</v>
@@ -2376,13 +2376,13 @@
         <v>-5</v>
       </c>
       <c r="I20" t="n">
-        <v>44</v>
+        <v>44.36</v>
       </c>
       <c r="J20" t="n">
         <v>41.58</v>
       </c>
       <c r="K20" t="n">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="L20" t="n">
         <v>71.79000000000001</v>
@@ -2473,13 +2473,13 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>269.85</v>
+        <v>267.4</v>
       </c>
       <c r="J21" t="n">
         <v>259.74</v>
       </c>
       <c r="K21" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="L21" t="n">
         <v>70.09</v>
@@ -2667,13 +2667,13 @@
         <v>-3</v>
       </c>
       <c r="I23" t="n">
-        <v>300</v>
+        <v>300.4</v>
       </c>
       <c r="J23" t="n">
         <v>311.69</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.8</v>
+        <v>-3.6</v>
       </c>
       <c r="L23" t="n">
         <v>63.24</v>
@@ -2764,13 +2764,13 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>113.45</v>
+        <v>113.68</v>
       </c>
       <c r="J24" t="n">
         <v>105.19</v>
       </c>
       <c r="K24" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="L24" t="n">
         <v>67.15000000000001</v>
@@ -2861,13 +2861,13 @@
         <v>-2</v>
       </c>
       <c r="I25" t="n">
-        <v>215.05</v>
+        <v>218.11</v>
       </c>
       <c r="J25" t="n">
         <v>208.31</v>
       </c>
       <c r="K25" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="L25" t="n">
         <v>67.04000000000001</v>
@@ -2958,13 +2958,13 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>273.35</v>
+        <v>273.7</v>
       </c>
       <c r="J26" t="n">
         <v>269.7</v>
       </c>
       <c r="K26" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="L26" t="n">
         <v>73.09</v>
@@ -3055,13 +3055,13 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>322</v>
+        <v>321.55</v>
       </c>
       <c r="J27" t="n">
         <v>297.3</v>
       </c>
       <c r="K27" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L27" t="n">
         <v>67.69</v>
@@ -3152,13 +3152,13 @@
         <v>-3</v>
       </c>
       <c r="I28" t="n">
-        <v>13.55</v>
+        <v>13.58</v>
       </c>
       <c r="J28" t="n">
         <v>11.97</v>
       </c>
       <c r="K28" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="L28" t="n">
         <v>69.12</v>
@@ -3245,13 +3245,13 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>444</v>
+        <v>441.85</v>
       </c>
       <c r="J29" t="n">
         <v>474.82</v>
       </c>
       <c r="K29" t="n">
-        <v>-6.5</v>
+        <v>-6.9</v>
       </c>
       <c r="L29" t="n">
         <v>70.55</v>
@@ -3342,13 +3342,13 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>161</v>
+        <v>161.73</v>
       </c>
       <c r="J30" t="n">
         <v>204.13</v>
       </c>
       <c r="K30" t="n">
-        <v>-21.1</v>
+        <v>-20.8</v>
       </c>
       <c r="L30" t="n">
         <v>64.08</v>
@@ -3439,13 +3439,13 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>526.4</v>
+        <v>526.2</v>
       </c>
       <c r="J31" t="n">
         <v>545.03</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.4</v>
+        <v>-3.5</v>
       </c>
       <c r="L31" t="n">
         <v>69.90000000000001</v>
@@ -3536,13 +3536,13 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>118.49</v>
+        <v>118.6</v>
       </c>
       <c r="J32" t="n">
         <v>114.86</v>
       </c>
       <c r="K32" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L32" t="n">
         <v>69.73999999999999</v>
@@ -3633,13 +3633,13 @@
         <v>-3</v>
       </c>
       <c r="I33" t="n">
-        <v>26</v>
+        <v>25.95</v>
       </c>
       <c r="J33" t="n">
         <v>29.14</v>
       </c>
       <c r="K33" t="n">
-        <v>-10.8</v>
+        <v>-10.9</v>
       </c>
       <c r="L33" t="n">
         <v>69.03</v>
@@ -3819,13 +3819,13 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>91.43000000000001</v>
+        <v>91.64</v>
       </c>
       <c r="J35" t="n">
         <v>88.06999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="L35" t="n">
         <v>70.88</v>
@@ -3916,13 +3916,13 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>70.40000000000001</v>
+        <v>70.48</v>
       </c>
       <c r="J36" t="n">
         <v>64.04000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="L36" t="n">
         <v>64.29000000000001</v>
@@ -4003,13 +4003,13 @@
         <v>-2</v>
       </c>
       <c r="I37" t="n">
-        <v>54.5</v>
+        <v>54.81</v>
       </c>
       <c r="J37" t="n">
         <v>53.44</v>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="L37" t="n">
         <v>67.23</v>
@@ -4098,13 +4098,13 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>75.16</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="J38" t="n">
         <v>74.92</v>
       </c>
       <c r="K38" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="L38" t="n">
         <v>62.78</v>
@@ -4195,13 +4195,13 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>164.99</v>
+        <v>163.53</v>
       </c>
       <c r="J39" t="n">
         <v>182.69</v>
       </c>
       <c r="K39" t="n">
-        <v>-9.699999999999999</v>
+        <v>-10.5</v>
       </c>
       <c r="L39" t="n">
         <v>69.05</v>
@@ -4290,7 +4290,7 @@
         <v>-2</v>
       </c>
       <c r="I40" t="n">
-        <v>57.01</v>
+        <v>57.04</v>
       </c>
       <c r="J40" t="n">
         <v>60.15</v>
@@ -4387,13 +4387,13 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>89.58</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="J41" t="n">
         <v>95.54000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>-6.2</v>
+        <v>-5.5</v>
       </c>
       <c r="L41" t="n">
         <v>71.72</v>
@@ -4484,13 +4484,13 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>169.62</v>
+        <v>169.46</v>
       </c>
       <c r="J42" t="n">
         <v>173.91</v>
       </c>
       <c r="K42" t="n">
-        <v>-2.5</v>
+        <v>-2.6</v>
       </c>
       <c r="L42" t="n">
         <v>65.64</v>
@@ -4581,13 +4581,13 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>274</v>
+        <v>272.7</v>
       </c>
       <c r="J43" t="n">
         <v>292.28</v>
       </c>
       <c r="K43" t="n">
-        <v>-6.3</v>
+        <v>-6.7</v>
       </c>
       <c r="L43" t="n">
         <v>70.45</v>
@@ -4775,13 +4775,13 @@
         <v>-2</v>
       </c>
       <c r="I45" t="n">
-        <v>110.9</v>
+        <v>111.53</v>
       </c>
       <c r="J45" t="n">
         <v>114.82</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.4</v>
+        <v>-2.9</v>
       </c>
       <c r="L45" t="n">
         <v>73.48</v>
@@ -4872,13 +4872,13 @@
         <v>-2</v>
       </c>
       <c r="I46" t="n">
-        <v>87</v>
+        <v>86.3</v>
       </c>
       <c r="J46" t="n">
         <v>100.33</v>
       </c>
       <c r="K46" t="n">
-        <v>-13.3</v>
+        <v>-14</v>
       </c>
       <c r="L46" t="n">
         <v>71.89</v>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>256</v>
+        <v>256.62</v>
       </c>
       <c r="D2" t="n">
         <v>158.6</v>
       </c>
       <c r="E2" t="n">
-        <v>61.4</v>
+        <v>61.8</v>
       </c>
       <c r="F2" t="n">
         <v>64.63</v>
@@ -5056,13 +5056,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>88</v>
+        <v>89.12</v>
       </c>
       <c r="D3" t="n">
         <v>55.67</v>
       </c>
       <c r="E3" t="n">
-        <v>58.1</v>
+        <v>60.1</v>
       </c>
       <c r="F3" t="n">
         <v>67.45999999999999</v>
@@ -5091,13 +5091,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5484</v>
+        <v>5493.5</v>
       </c>
       <c r="D4" t="n">
         <v>5085.36</v>
       </c>
       <c r="E4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
         <v>67.16</v>
@@ -5126,13 +5126,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1960</v>
+        <v>1963.4</v>
       </c>
       <c r="D5" t="n">
         <v>920.51</v>
       </c>
       <c r="E5" t="n">
-        <v>112.9</v>
+        <v>113.3</v>
       </c>
       <c r="F5" t="n">
         <v>73.16</v>
@@ -5161,13 +5161,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>822.3</v>
+        <v>816.9</v>
       </c>
       <c r="D6" t="n">
         <v>753.55</v>
       </c>
       <c r="E6" t="n">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="F6" t="n">
         <v>69.61</v>
@@ -5231,13 +5231,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>368.5</v>
+        <v>371.75</v>
       </c>
       <c r="D8" t="n">
         <v>335.41</v>
       </c>
       <c r="E8" t="n">
-        <v>9.9</v>
+        <v>10.8</v>
       </c>
       <c r="F8" t="n">
         <v>68.48</v>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>67.88</v>
+        <v>68.55</v>
       </c>
       <c r="D9" t="n">
         <v>70.27</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.4</v>
+        <v>-2.4</v>
       </c>
       <c r="F9" t="n">
         <v>72.56999999999999</v>
@@ -5301,13 +5301,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>547.45</v>
+        <v>541.05</v>
       </c>
       <c r="D10" t="n">
         <v>390.61</v>
       </c>
       <c r="E10" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="F10" t="n">
         <v>63.09</v>
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>193.72</v>
       </c>
       <c r="D11" t="n">
         <v>164.1</v>
       </c>
       <c r="E11" t="n">
-        <v>15.8</v>
+        <v>18</v>
       </c>
       <c r="F11" t="n">
         <v>60.6</v>
@@ -5371,13 +5371,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>372.1</v>
+        <v>376.15</v>
       </c>
       <c r="D12" t="n">
         <v>338.1</v>
       </c>
       <c r="E12" t="n">
-        <v>10.1</v>
+        <v>11.3</v>
       </c>
       <c r="F12" t="n">
         <v>66.73</v>
@@ -5406,13 +5406,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>625</v>
+        <v>617.6</v>
       </c>
       <c r="D13" t="n">
         <v>558.6799999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>11.9</v>
+        <v>10.5</v>
       </c>
       <c r="F13" t="n">
         <v>64.68000000000001</v>
@@ -5476,13 +5476,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>271</v>
+        <v>273.91</v>
       </c>
       <c r="D15" t="n">
         <v>230</v>
       </c>
       <c r="E15" t="n">
-        <v>17.8</v>
+        <v>19.1</v>
       </c>
       <c r="F15" t="n">
         <v>67.65000000000001</v>
@@ -5511,13 +5511,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20.4</v>
+        <v>20.09</v>
       </c>
       <c r="D16" t="n">
         <v>21.01</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.9</v>
+        <v>-4.4</v>
       </c>
       <c r="F16" t="n">
         <v>70.87</v>
@@ -5546,13 +5546,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>131.15</v>
+        <v>132.32</v>
       </c>
       <c r="D17" t="n">
         <v>100.9</v>
       </c>
       <c r="E17" t="n">
-        <v>30</v>
+        <v>31.1</v>
       </c>
       <c r="F17" t="n">
         <v>69.56</v>
@@ -5581,13 +5581,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>774.5</v>
+        <v>770.35</v>
       </c>
       <c r="D18" t="n">
         <v>716.01</v>
       </c>
       <c r="E18" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="F18" t="n">
         <v>61.71</v>
@@ -5616,13 +5616,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>112.5</v>
+        <v>113.43</v>
       </c>
       <c r="D19" t="n">
         <v>109.31</v>
       </c>
       <c r="E19" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="F19" t="n">
         <v>72.34</v>
@@ -5651,13 +5651,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>44</v>
+        <v>44.36</v>
       </c>
       <c r="D20" t="n">
         <v>41.58</v>
       </c>
       <c r="E20" t="n">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="F20" t="n">
         <v>71.79000000000001</v>
@@ -5686,13 +5686,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>269.85</v>
+        <v>267.4</v>
       </c>
       <c r="D21" t="n">
         <v>259.74</v>
       </c>
       <c r="E21" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="F21" t="n">
         <v>70.09</v>
@@ -5756,13 +5756,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>300</v>
+        <v>300.4</v>
       </c>
       <c r="D23" t="n">
         <v>311.69</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8</v>
+        <v>-3.6</v>
       </c>
       <c r="F23" t="n">
         <v>63.24</v>
@@ -5791,13 +5791,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>113.45</v>
+        <v>113.68</v>
       </c>
       <c r="D24" t="n">
         <v>105.19</v>
       </c>
       <c r="E24" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="F24" t="n">
         <v>67.15000000000001</v>
@@ -5826,13 +5826,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>215.05</v>
+        <v>218.11</v>
       </c>
       <c r="D25" t="n">
         <v>208.31</v>
       </c>
       <c r="E25" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="F25" t="n">
         <v>67.04000000000001</v>
@@ -5861,13 +5861,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>273.35</v>
+        <v>273.7</v>
       </c>
       <c r="D26" t="n">
         <v>269.7</v>
       </c>
       <c r="E26" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F26" t="n">
         <v>73.09</v>
@@ -5896,13 +5896,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>322</v>
+        <v>321.55</v>
       </c>
       <c r="D27" t="n">
         <v>297.3</v>
       </c>
       <c r="E27" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F27" t="n">
         <v>67.69</v>
@@ -5931,13 +5931,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>13.55</v>
+        <v>13.58</v>
       </c>
       <c r="D28" t="n">
         <v>11.97</v>
       </c>
       <c r="E28" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="F28" t="n">
         <v>69.12</v>
@@ -5966,13 +5966,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>444</v>
+        <v>441.85</v>
       </c>
       <c r="D29" t="n">
         <v>474.82</v>
       </c>
       <c r="E29" t="n">
-        <v>-6.5</v>
+        <v>-6.9</v>
       </c>
       <c r="F29" t="n">
         <v>70.55</v>
@@ -6001,13 +6001,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>161</v>
+        <v>161.73</v>
       </c>
       <c r="D30" t="n">
         <v>204.13</v>
       </c>
       <c r="E30" t="n">
-        <v>-21.1</v>
+        <v>-20.8</v>
       </c>
       <c r="F30" t="n">
         <v>64.08</v>
@@ -6036,13 +6036,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>526.4</v>
+        <v>526.2</v>
       </c>
       <c r="D31" t="n">
         <v>545.03</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.4</v>
+        <v>-3.5</v>
       </c>
       <c r="F31" t="n">
         <v>69.90000000000001</v>
@@ -6071,13 +6071,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>118.49</v>
+        <v>118.6</v>
       </c>
       <c r="D32" t="n">
         <v>114.86</v>
       </c>
       <c r="E32" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="F32" t="n">
         <v>69.73999999999999</v>
@@ -6106,13 +6106,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>26</v>
+        <v>25.95</v>
       </c>
       <c r="D33" t="n">
         <v>29.14</v>
       </c>
       <c r="E33" t="n">
-        <v>-10.8</v>
+        <v>-10.9</v>
       </c>
       <c r="F33" t="n">
         <v>69.03</v>
@@ -6176,13 +6176,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>91.43000000000001</v>
+        <v>91.64</v>
       </c>
       <c r="D35" t="n">
         <v>88.06999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="F35" t="n">
         <v>70.88</v>
@@ -6211,13 +6211,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>70.40000000000001</v>
+        <v>70.48</v>
       </c>
       <c r="D36" t="n">
         <v>64.04000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="F36" t="n">
         <v>64.29000000000001</v>
@@ -6246,13 +6246,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>54.5</v>
+        <v>54.81</v>
       </c>
       <c r="D37" t="n">
         <v>53.44</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="F37" t="n">
         <v>67.23</v>
@@ -6281,13 +6281,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>75.16</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="D38" t="n">
         <v>74.92</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F38" t="n">
         <v>62.78</v>
@@ -6316,13 +6316,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>164.99</v>
+        <v>163.53</v>
       </c>
       <c r="D39" t="n">
         <v>182.69</v>
       </c>
       <c r="E39" t="n">
-        <v>-9.699999999999999</v>
+        <v>-10.5</v>
       </c>
       <c r="F39" t="n">
         <v>69.05</v>
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>57.01</v>
+        <v>57.04</v>
       </c>
       <c r="D40" t="n">
         <v>60.15</v>
@@ -6386,13 +6386,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>89.58</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="D41" t="n">
         <v>95.54000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>-6.2</v>
+        <v>-5.5</v>
       </c>
       <c r="F41" t="n">
         <v>71.72</v>
@@ -6421,13 +6421,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>169.62</v>
+        <v>169.46</v>
       </c>
       <c r="D42" t="n">
         <v>173.91</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.5</v>
+        <v>-2.6</v>
       </c>
       <c r="F42" t="n">
         <v>65.64</v>
@@ -6456,13 +6456,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>274</v>
+        <v>272.7</v>
       </c>
       <c r="D43" t="n">
         <v>292.28</v>
       </c>
       <c r="E43" t="n">
-        <v>-6.3</v>
+        <v>-6.7</v>
       </c>
       <c r="F43" t="n">
         <v>70.45</v>
@@ -6526,13 +6526,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>110.9</v>
+        <v>111.53</v>
       </c>
       <c r="D45" t="n">
         <v>114.82</v>
       </c>
       <c r="E45" t="n">
-        <v>-3.4</v>
+        <v>-2.9</v>
       </c>
       <c r="F45" t="n">
         <v>73.48</v>
@@ -6561,13 +6561,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>87</v>
+        <v>86.3</v>
       </c>
       <c r="D46" t="n">
         <v>100.33</v>
       </c>
       <c r="E46" t="n">
-        <v>-13.3</v>
+        <v>-14</v>
       </c>
       <c r="F46" t="n">
         <v>71.89</v>
@@ -6617,7 +6617,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -6627,7 +6627,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -6647,7 +6647,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
